--- a/xls/square_12_tri3_14.xlsx
+++ b/xls/square_12_tri3_14.xlsx
@@ -418,7 +418,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAF0E20E-E4D8-9B45-9C94-E89B574F109C}">
-  <dimension ref="A1:K24"/>
+  <dimension ref="A1:K32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -482,13 +482,13 @@
         <v>1176</v>
       </c>
       <c r="I14">
-        <v>0.46750691584795095</v>
+        <v>0.46751064931818076</v>
       </c>
       <c r="J14">
-        <v>-1.7521719431806217</v>
+        <v>-1.752170790702204</v>
       </c>
       <c r="K14">
-        <v>0.29129682724447536</v>
+        <v>0.29127235765722337</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -517,13 +517,13 @@
         <v>1350</v>
       </c>
       <c r="I15">
-        <v>-2.2370649853538223</v>
+        <v>-2.2370645777312754</v>
       </c>
       <c r="J15">
-        <v>-1.77223726353443</v>
+        <v>-1.7722373805310954</v>
       </c>
       <c r="K15">
-        <v>1.7464367673476422</v>
+        <v>1.7464360947094872</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -552,13 +552,13 @@
         <v>1536</v>
       </c>
       <c r="I16">
-        <v>-1.9208572183281762</v>
+        <v>-1.9208567142749517</v>
       </c>
       <c r="J16">
-        <v>-1.520774858016234</v>
+        <v>-1.5207748962493441</v>
       </c>
       <c r="K16">
-        <v>2.5822107236077185</v>
+        <v>2.582210691836875</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -587,13 +587,13 @@
         <v>1734</v>
       </c>
       <c r="I17">
-        <v>-1.1430032840753594</v>
+        <v>-1.1430032373652756</v>
       </c>
       <c r="J17">
-        <v>-0.9303595005143546</v>
+        <v>-0.9303594784393188</v>
       </c>
       <c r="K17">
-        <v>3.6740552565999516</v>
+        <v>3.6740552539775924</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -622,13 +622,13 @@
         <v>1944</v>
       </c>
       <c r="I18">
-        <v>-0.3330404591310055</v>
+        <v>-0.33304045924097075</v>
       </c>
       <c r="J18">
-        <v>-0.29365354465257676</v>
+        <v>-0.2936535443500486</v>
       </c>
       <c r="K18">
-        <v>3.9452483765768602</v>
+        <v>3.9452483753118575</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -657,13 +657,13 @@
         <v>2166</v>
       </c>
       <c r="I19">
-        <v>0.0008124697325477483</v>
+        <v>0.0008124697565817115</v>
       </c>
       <c r="J19">
-        <v>-0.00025582187740608376</v>
+        <v>-0.0002558218658645324</v>
       </c>
       <c r="K19">
-        <v>3.007226710181981</v>
+        <v>3.007226710573176</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -692,13 +692,13 @@
         <v>2400</v>
       </c>
       <c r="I20">
-        <v>-0.0007605960473485355</v>
+        <v>-0.000760596047303664</v>
       </c>
       <c r="J20">
-        <v>-0.000554625301836055</v>
+        <v>-0.000554625301818868</v>
       </c>
       <c r="K20">
-        <v>2.6968927695286498</v>
+        <v>2.6968927695832106</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -727,13 +727,13 @@
         <v>2646</v>
       </c>
       <c r="I21">
-        <v>-0.0013229866051862635</v>
+        <v>-0.0013229866045252798</v>
       </c>
       <c r="J21">
-        <v>-0.000891450437170025</v>
+        <v>-0.0008914504367254263</v>
       </c>
       <c r="K21">
-        <v>2.730016401672519</v>
+        <v>2.7300164015036796</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -762,13 +762,13 @@
         <v>2904</v>
       </c>
       <c r="I22">
-        <v>-0.00023550423084927753</v>
+        <v>-0.00023550423087031127</v>
       </c>
       <c r="J22">
-        <v>-0.0001841024622379999</v>
+        <v>-0.00018410246225343568</v>
       </c>
       <c r="K22">
-        <v>2.489635551191578</v>
+        <v>2.4896355514667055</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -797,13 +797,13 @@
         <v>3174</v>
       </c>
       <c r="I23">
-        <v>-4.1490480897573334e-5</v>
+        <v>-4.149048089834487e-5</v>
       </c>
       <c r="J23">
-        <v>-3.298759286250758e-5</v>
+        <v>-3.298759286313444e-5</v>
       </c>
       <c r="K23">
-        <v>2.1427869857496487</v>
+        <v>2.1427869859891255</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -832,13 +832,293 @@
         <v>3456</v>
       </c>
       <c r="I24">
-        <v>-0.00025551829491504653</v>
+        <v>-0.000255518294906459</v>
       </c>
       <c r="J24">
-        <v>-0.00020368494464681057</v>
+        <v>-0.00020368494464111838</v>
       </c>
       <c r="K24">
-        <v>2.521215358154015</v>
+        <v>2.5212153579366965</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11">
+      <c r="A25" t="s">
+        <v>11</v>
+      </c>
+      <c r="B25">
+        <v>225</v>
+      </c>
+      <c r="C25" t="s">
+        <v>11</v>
+      </c>
+      <c r="D25">
+        <v>169</v>
+      </c>
+      <c r="E25" t="s">
+        <v>12</v>
+      </c>
+      <c r="F25">
+        <v>676</v>
+      </c>
+      <c r="G25" t="s">
+        <v>13</v>
+      </c>
+      <c r="H25">
+        <v>3750</v>
+      </c>
+      <c r="I25">
+        <v>1.0417472432465434e-6</v>
+      </c>
+      <c r="J25">
+        <v>-6.0143993092253534e-6</v>
+      </c>
+      <c r="K25">
+        <v>2.0565151826373396</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11">
+      <c r="A26" t="s">
+        <v>11</v>
+      </c>
+      <c r="B26">
+        <v>225</v>
+      </c>
+      <c r="C26" t="s">
+        <v>11</v>
+      </c>
+      <c r="D26">
+        <v>169</v>
+      </c>
+      <c r="E26" t="s">
+        <v>12</v>
+      </c>
+      <c r="F26">
+        <v>729</v>
+      </c>
+      <c r="G26" t="s">
+        <v>13</v>
+      </c>
+      <c r="H26">
+        <v>4056</v>
+      </c>
+      <c r="I26">
+        <v>-0.00025245025127139636</v>
+      </c>
+      <c r="J26">
+        <v>-0.00020050558498218486</v>
+      </c>
+      <c r="K26">
+        <v>2.5188381200502867</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11">
+      <c r="A27" t="s">
+        <v>11</v>
+      </c>
+      <c r="B27">
+        <v>225</v>
+      </c>
+      <c r="C27" t="s">
+        <v>11</v>
+      </c>
+      <c r="D27">
+        <v>169</v>
+      </c>
+      <c r="E27" t="s">
+        <v>12</v>
+      </c>
+      <c r="F27">
+        <v>784</v>
+      </c>
+      <c r="G27" t="s">
+        <v>13</v>
+      </c>
+      <c r="H27">
+        <v>4374</v>
+      </c>
+      <c r="I27">
+        <v>1.0740162994003845e-5</v>
+      </c>
+      <c r="J27">
+        <v>2.1808316661879946e-6</v>
+      </c>
+      <c r="K27">
+        <v>1.9021822384194813</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11">
+      <c r="A28" t="s">
+        <v>11</v>
+      </c>
+      <c r="B28">
+        <v>225</v>
+      </c>
+      <c r="C28" t="s">
+        <v>11</v>
+      </c>
+      <c r="D28">
+        <v>169</v>
+      </c>
+      <c r="E28" t="s">
+        <v>12</v>
+      </c>
+      <c r="F28">
+        <v>841</v>
+      </c>
+      <c r="G28" t="s">
+        <v>13</v>
+      </c>
+      <c r="H28">
+        <v>4704</v>
+      </c>
+      <c r="I28">
+        <v>-2.6730657588300144e-5</v>
+      </c>
+      <c r="J28">
+        <v>-1.6768565006435775e-5</v>
+      </c>
+      <c r="K28">
+        <v>1.813547432248889</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11">
+      <c r="A29" t="s">
+        <v>11</v>
+      </c>
+      <c r="B29">
+        <v>225</v>
+      </c>
+      <c r="C29" t="s">
+        <v>11</v>
+      </c>
+      <c r="D29">
+        <v>169</v>
+      </c>
+      <c r="E29" t="s">
+        <v>12</v>
+      </c>
+      <c r="F29">
+        <v>900</v>
+      </c>
+      <c r="G29" t="s">
+        <v>13</v>
+      </c>
+      <c r="H29">
+        <v>5046</v>
+      </c>
+      <c r="I29">
+        <v>-1.5096936989503904e-7</v>
+      </c>
+      <c r="J29">
+        <v>-2.3203493307021482e-7</v>
+      </c>
+      <c r="K29">
+        <v>1.2196371049729848</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11">
+      <c r="A30" t="s">
+        <v>11</v>
+      </c>
+      <c r="B30">
+        <v>225</v>
+      </c>
+      <c r="C30" t="s">
+        <v>11</v>
+      </c>
+      <c r="D30">
+        <v>169</v>
+      </c>
+      <c r="E30" t="s">
+        <v>12</v>
+      </c>
+      <c r="F30">
+        <v>961</v>
+      </c>
+      <c r="G30" t="s">
+        <v>13</v>
+      </c>
+      <c r="H30">
+        <v>5400</v>
+      </c>
+      <c r="I30">
+        <v>-6.500741826627519e-7</v>
+      </c>
+      <c r="J30">
+        <v>-5.395246998829348e-7</v>
+      </c>
+      <c r="K30">
+        <v>1.260208073640029</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11">
+      <c r="A31" t="s">
+        <v>11</v>
+      </c>
+      <c r="B31">
+        <v>225</v>
+      </c>
+      <c r="C31" t="s">
+        <v>11</v>
+      </c>
+      <c r="D31">
+        <v>169</v>
+      </c>
+      <c r="E31" t="s">
+        <v>12</v>
+      </c>
+      <c r="F31">
+        <v>1024</v>
+      </c>
+      <c r="G31" t="s">
+        <v>13</v>
+      </c>
+      <c r="H31">
+        <v>5766</v>
+      </c>
+      <c r="I31">
+        <v>-4.394766712938213e-7</v>
+      </c>
+      <c r="J31">
+        <v>-3.5685381604649337e-7</v>
+      </c>
+      <c r="K31">
+        <v>1.1660930416270376</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11">
+      <c r="A32" t="s">
+        <v>11</v>
+      </c>
+      <c r="B32">
+        <v>225</v>
+      </c>
+      <c r="C32" t="s">
+        <v>11</v>
+      </c>
+      <c r="D32">
+        <v>169</v>
+      </c>
+      <c r="E32" t="s">
+        <v>12</v>
+      </c>
+      <c r="F32">
+        <v>1089</v>
+      </c>
+      <c r="G32" t="s">
+        <v>13</v>
+      </c>
+      <c r="H32">
+        <v>6144</v>
+      </c>
+      <c r="I32">
+        <v>-3.890411055470321e-7</v>
+      </c>
+      <c r="J32">
+        <v>-3.2867989840005446e-7</v>
+      </c>
+      <c r="K32">
+        <v>1.1598917028319093</v>
       </c>
     </row>
   </sheetData>

--- a/xls/square_12_tri3_14.xlsx
+++ b/xls/square_12_tri3_14.xlsx
@@ -456,6 +456,76 @@
         <v>10</v>
       </c>
     </row>
+    <row r="12" spans="1:11">
+      <c r="A12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>225</v>
+      </c>
+      <c r="C12" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12">
+        <v>169</v>
+      </c>
+      <c r="E12" t="s">
+        <v>12</v>
+      </c>
+      <c r="F12">
+        <v>169</v>
+      </c>
+      <c r="G12" t="s">
+        <v>13</v>
+      </c>
+      <c r="H12">
+        <v>864</v>
+      </c>
+      <c r="I12">
+        <v>4.32485319870614</v>
+      </c>
+      <c r="J12">
+        <v>0.6256180521661772</v>
+      </c>
+      <c r="K12">
+        <v>1.506955399021566</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13">
+        <v>225</v>
+      </c>
+      <c r="C13" t="s">
+        <v>11</v>
+      </c>
+      <c r="D13">
+        <v>169</v>
+      </c>
+      <c r="E13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F13">
+        <v>196</v>
+      </c>
+      <c r="G13" t="s">
+        <v>13</v>
+      </c>
+      <c r="H13">
+        <v>1014</v>
+      </c>
+      <c r="I13">
+        <v>2.58272444804612</v>
+      </c>
+      <c r="J13">
+        <v>-0.5283142593710451</v>
+      </c>
+      <c r="K13">
+        <v>3.00613984892567</v>
+      </c>
+    </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
         <v>11</v>
